--- a/outputs/55049.xlsx
+++ b/outputs/55049.xlsx
@@ -583,8 +583,8 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A3)*(book2!H:J))</f>
-        <v>7040</v>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A3)*(book2!H:J&gt;0))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -592,7 +592,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A4)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A4)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -601,7 +601,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A5)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A5)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -610,7 +610,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A6)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A6)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -619,7 +619,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A7)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A7)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -628,7 +628,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A8)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A8)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -637,7 +637,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A9)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A9)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -646,7 +646,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A10)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A10)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -655,8 +655,8 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A11)*(book2!H:J))</f>
-        <v>121</v>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A11)*(book2!H:J&gt;0))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -664,7 +664,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A12)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A12)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -673,7 +673,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A13)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A13)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -682,7 +682,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A14)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A14)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -691,7 +691,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A15)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A15)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -700,7 +700,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A16)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A16)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -709,8 +709,8 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A17)*(book2!H:J))</f>
-        <v>77</v>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A17)*(book2!H:J&gt;0))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -718,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A18)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A18)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -727,7 +727,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A19)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A19)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -736,8 +736,8 @@
         <v>18</v>
       </c>
       <c r="B20" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A20)*(book2!H:J))</f>
-        <v>11162</v>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A20)*(book2!H:J&gt;0))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -745,7 +745,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A21)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A21)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -754,7 +754,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A22)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A22)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -763,7 +763,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="n">
-        <f aca="false">SUMPRODUCT((book2!A:A=book1!A23)*(book2!H:J))</f>
+        <f aca="false">SUMPRODUCT((book2!A:A=book1!A23)*(book2!H:J&gt;0))</f>
         <v>0</v>
       </c>
     </row>
